--- a/docs/screenshots/akpass/local/chromium-association.xlsx
+++ b/docs/screenshots/akpass/local/chromium-association.xlsx
@@ -697,7 +697,7 @@
       <c r="T7" s="0"/>
       <c r="U7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">15/09/2026</t>
+          <t xml:space="preserve">16/09/2026</t>
         </is>
       </c>
     </row>
